--- a/課題管理表/課題管理表_20260304.xlsx
+++ b/課題管理表/課題管理表_20260304.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\jst_fujiwara\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FileManagementSystem_Doc\課題管理表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEBA860-2C57-47D2-A046-93A156A16A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE7992F-9378-4DF0-A9A4-0063EB1A1EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4035" yWindow="3210" windowWidth="21360" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="課題管理表" sheetId="13" r:id="rId1"/>
@@ -2960,6 +2960,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3047,15 +3065,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3091,15 +3100,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3361,137 +3361,137 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7374263A-109B-4CCF-9763-03440C8899FF}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:BS80"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.33203125" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="1"/>
+    <col min="1" max="1" width="3.33203125" style="1"/>
     <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="36" width="3.28515625" style="1"/>
-    <col min="37" max="40" width="3.28515625" style="16"/>
-    <col min="41" max="42" width="3.28515625" style="1"/>
-    <col min="43" max="50" width="3.28515625" style="2"/>
-    <col min="51" max="51" width="5.5703125" style="2" customWidth="1"/>
+    <col min="3" max="36" width="3.33203125" style="1"/>
+    <col min="37" max="40" width="3.33203125" style="16"/>
+    <col min="41" max="42" width="3.33203125" style="1"/>
+    <col min="43" max="50" width="3.33203125" style="2"/>
+    <col min="51" max="51" width="5.5546875" style="2" customWidth="1"/>
     <col min="52" max="52" width="12" style="2" customWidth="1"/>
-    <col min="53" max="53" width="10.7109375" style="2" customWidth="1"/>
-    <col min="54" max="54" width="11.28515625" style="2" customWidth="1"/>
-    <col min="55" max="16384" width="3.28515625" style="2"/>
+    <col min="53" max="53" width="10.6640625" style="2" customWidth="1"/>
+    <col min="54" max="54" width="11.33203125" style="2" customWidth="1"/>
+    <col min="55" max="16384" width="3.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:71" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:71" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="72" t="s">
+    <row r="1" spans="2:71" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:71" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="74" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="74" t="s">
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
-      <c r="W2" s="75"/>
-      <c r="X2" s="75"/>
-      <c r="Y2" s="75"/>
-      <c r="Z2" s="75"/>
-      <c r="AA2" s="75"/>
-      <c r="AB2" s="76"/>
-      <c r="AC2" s="74" t="s">
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="81"/>
+      <c r="AB2" s="82"/>
+      <c r="AC2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="AD2" s="75"/>
-      <c r="AE2" s="75"/>
-      <c r="AF2" s="75"/>
-      <c r="AG2" s="75"/>
-      <c r="AH2" s="75"/>
-      <c r="AI2" s="75"/>
-      <c r="AJ2" s="75"/>
-      <c r="AK2" s="75"/>
-      <c r="AL2" s="75"/>
-      <c r="AM2" s="75"/>
-      <c r="AN2" s="75"/>
-      <c r="AO2" s="75"/>
-      <c r="AP2" s="76"/>
-      <c r="AQ2" s="73" t="s">
+      <c r="AD2" s="81"/>
+      <c r="AE2" s="81"/>
+      <c r="AF2" s="81"/>
+      <c r="AG2" s="81"/>
+      <c r="AH2" s="81"/>
+      <c r="AI2" s="81"/>
+      <c r="AJ2" s="81"/>
+      <c r="AK2" s="81"/>
+      <c r="AL2" s="81"/>
+      <c r="AM2" s="81"/>
+      <c r="AN2" s="81"/>
+      <c r="AO2" s="81"/>
+      <c r="AP2" s="82"/>
+      <c r="AQ2" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="AR2" s="73"/>
-      <c r="AS2" s="73"/>
-      <c r="AT2" s="73"/>
-      <c r="AU2" s="72" t="s">
+      <c r="AR2" s="79"/>
+      <c r="AS2" s="79"/>
+      <c r="AT2" s="79"/>
+      <c r="AU2" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="AV2" s="72"/>
-      <c r="AW2" s="72"/>
-      <c r="AX2" s="72"/>
-    </row>
-    <row r="3" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
-      <c r="Z3" s="78"/>
-      <c r="AA3" s="78"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="77"/>
-      <c r="AD3" s="78"/>
-      <c r="AE3" s="78"/>
-      <c r="AF3" s="78"/>
-      <c r="AG3" s="78"/>
-      <c r="AH3" s="78"/>
-      <c r="AI3" s="78"/>
-      <c r="AJ3" s="78"/>
-      <c r="AK3" s="78"/>
-      <c r="AL3" s="78"/>
-      <c r="AM3" s="78"/>
-      <c r="AN3" s="78"/>
-      <c r="AO3" s="78"/>
-      <c r="AP3" s="79"/>
-      <c r="AQ3" s="73"/>
-      <c r="AR3" s="73"/>
-      <c r="AS3" s="73"/>
-      <c r="AT3" s="73"/>
-      <c r="AU3" s="72"/>
-      <c r="AV3" s="72"/>
-      <c r="AW3" s="72"/>
-      <c r="AX3" s="72"/>
+      <c r="AV2" s="78"/>
+      <c r="AW2" s="78"/>
+      <c r="AX2" s="78"/>
+    </row>
+    <row r="3" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="84"/>
+      <c r="Y3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="83"/>
+      <c r="AD3" s="84"/>
+      <c r="AE3" s="84"/>
+      <c r="AF3" s="84"/>
+      <c r="AG3" s="84"/>
+      <c r="AH3" s="84"/>
+      <c r="AI3" s="84"/>
+      <c r="AJ3" s="84"/>
+      <c r="AK3" s="84"/>
+      <c r="AL3" s="84"/>
+      <c r="AM3" s="84"/>
+      <c r="AN3" s="84"/>
+      <c r="AO3" s="84"/>
+      <c r="AP3" s="85"/>
+      <c r="AQ3" s="79"/>
+      <c r="AR3" s="79"/>
+      <c r="AS3" s="79"/>
+      <c r="AT3" s="79"/>
+      <c r="AU3" s="78"/>
+      <c r="AV3" s="78"/>
+      <c r="AW3" s="78"/>
+      <c r="AX3" s="78"/>
       <c r="BN3" s="2" t="s">
         <v>92</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3">
         <v>2</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="3">
         <v>5</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="3">
         <v>6</v>
       </c>
@@ -3916,7 +3916,7 @@
       <c r="AW9" s="7"/>
       <c r="AX9" s="8"/>
     </row>
-    <row r="10" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="3">
         <v>7</v>
       </c>
@@ -3981,7 +3981,7 @@
       <c r="AW10" s="7"/>
       <c r="AX10" s="8"/>
     </row>
-    <row r="11" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="3">
         <v>8</v>
       </c>
@@ -4046,7 +4046,7 @@
       <c r="AW11" s="7"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="3">
         <v>9</v>
       </c>
@@ -4111,8 +4111,8 @@
       <c r="AW12" s="7"/>
       <c r="AX12" s="8"/>
     </row>
-    <row r="13" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="80">
+    <row r="13" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="86">
         <v>10</v>
       </c>
       <c r="C13" s="51" t="s">
@@ -4163,21 +4163,21 @@
       <c r="AN13" s="42"/>
       <c r="AO13" s="42"/>
       <c r="AP13" s="43"/>
-      <c r="AQ13" s="83">
+      <c r="AQ13" s="89">
         <v>45609</v>
       </c>
-      <c r="AR13" s="84"/>
-      <c r="AS13" s="84"/>
-      <c r="AT13" s="85"/>
-      <c r="AU13" s="63" t="s">
+      <c r="AR13" s="90"/>
+      <c r="AS13" s="90"/>
+      <c r="AT13" s="91"/>
+      <c r="AU13" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="AV13" s="64"/>
-      <c r="AW13" s="64"/>
-      <c r="AX13" s="65"/>
-    </row>
-    <row r="14" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="81"/>
+      <c r="AV13" s="70"/>
+      <c r="AW13" s="70"/>
+      <c r="AX13" s="71"/>
+    </row>
+    <row r="14" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="87"/>
       <c r="C14" s="57"/>
       <c r="D14" s="58"/>
       <c r="E14" s="58"/>
@@ -4204,31 +4204,31 @@
       <c r="Z14" s="58"/>
       <c r="AA14" s="58"/>
       <c r="AB14" s="59"/>
-      <c r="AC14" s="107"/>
-      <c r="AD14" s="108"/>
-      <c r="AE14" s="108"/>
-      <c r="AF14" s="108"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="108"/>
-      <c r="AI14" s="108"/>
-      <c r="AJ14" s="108"/>
-      <c r="AK14" s="108"/>
-      <c r="AL14" s="108"/>
-      <c r="AM14" s="108"/>
-      <c r="AN14" s="108"/>
-      <c r="AO14" s="108"/>
-      <c r="AP14" s="109"/>
-      <c r="AQ14" s="86"/>
-      <c r="AR14" s="87"/>
-      <c r="AS14" s="87"/>
-      <c r="AT14" s="88"/>
-      <c r="AU14" s="66"/>
-      <c r="AV14" s="67"/>
-      <c r="AW14" s="67"/>
-      <c r="AX14" s="68"/>
-    </row>
-    <row r="15" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="81"/>
+      <c r="AC14" s="63"/>
+      <c r="AD14" s="64"/>
+      <c r="AE14" s="64"/>
+      <c r="AF14" s="64"/>
+      <c r="AG14" s="64"/>
+      <c r="AH14" s="64"/>
+      <c r="AI14" s="64"/>
+      <c r="AJ14" s="64"/>
+      <c r="AK14" s="64"/>
+      <c r="AL14" s="64"/>
+      <c r="AM14" s="64"/>
+      <c r="AN14" s="64"/>
+      <c r="AO14" s="64"/>
+      <c r="AP14" s="65"/>
+      <c r="AQ14" s="92"/>
+      <c r="AR14" s="93"/>
+      <c r="AS14" s="93"/>
+      <c r="AT14" s="94"/>
+      <c r="AU14" s="72"/>
+      <c r="AV14" s="73"/>
+      <c r="AW14" s="73"/>
+      <c r="AX14" s="74"/>
+    </row>
+    <row r="15" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="87"/>
       <c r="C15" s="57"/>
       <c r="D15" s="58"/>
       <c r="E15" s="58"/>
@@ -4255,31 +4255,31 @@
       <c r="Z15" s="58"/>
       <c r="AA15" s="58"/>
       <c r="AB15" s="59"/>
-      <c r="AC15" s="107"/>
-      <c r="AD15" s="108"/>
-      <c r="AE15" s="108"/>
-      <c r="AF15" s="108"/>
-      <c r="AG15" s="108"/>
-      <c r="AH15" s="108"/>
-      <c r="AI15" s="108"/>
-      <c r="AJ15" s="108"/>
-      <c r="AK15" s="108"/>
-      <c r="AL15" s="108"/>
-      <c r="AM15" s="108"/>
-      <c r="AN15" s="108"/>
-      <c r="AO15" s="108"/>
-      <c r="AP15" s="109"/>
-      <c r="AQ15" s="86"/>
-      <c r="AR15" s="87"/>
-      <c r="AS15" s="87"/>
-      <c r="AT15" s="88"/>
-      <c r="AU15" s="66"/>
-      <c r="AV15" s="67"/>
-      <c r="AW15" s="67"/>
-      <c r="AX15" s="68"/>
-    </row>
-    <row r="16" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="81"/>
+      <c r="AC15" s="63"/>
+      <c r="AD15" s="64"/>
+      <c r="AE15" s="64"/>
+      <c r="AF15" s="64"/>
+      <c r="AG15" s="64"/>
+      <c r="AH15" s="64"/>
+      <c r="AI15" s="64"/>
+      <c r="AJ15" s="64"/>
+      <c r="AK15" s="64"/>
+      <c r="AL15" s="64"/>
+      <c r="AM15" s="64"/>
+      <c r="AN15" s="64"/>
+      <c r="AO15" s="64"/>
+      <c r="AP15" s="65"/>
+      <c r="AQ15" s="92"/>
+      <c r="AR15" s="93"/>
+      <c r="AS15" s="93"/>
+      <c r="AT15" s="94"/>
+      <c r="AU15" s="72"/>
+      <c r="AV15" s="73"/>
+      <c r="AW15" s="73"/>
+      <c r="AX15" s="74"/>
+    </row>
+    <row r="16" spans="2:71" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="87"/>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
       <c r="E16" s="58"/>
@@ -4306,31 +4306,31 @@
       <c r="Z16" s="58"/>
       <c r="AA16" s="58"/>
       <c r="AB16" s="59"/>
-      <c r="AC16" s="107"/>
-      <c r="AD16" s="108"/>
-      <c r="AE16" s="108"/>
-      <c r="AF16" s="108"/>
-      <c r="AG16" s="108"/>
-      <c r="AH16" s="108"/>
-      <c r="AI16" s="108"/>
-      <c r="AJ16" s="108"/>
-      <c r="AK16" s="108"/>
-      <c r="AL16" s="108"/>
-      <c r="AM16" s="108"/>
-      <c r="AN16" s="108"/>
-      <c r="AO16" s="108"/>
-      <c r="AP16" s="109"/>
-      <c r="AQ16" s="86"/>
-      <c r="AR16" s="87"/>
-      <c r="AS16" s="87"/>
-      <c r="AT16" s="88"/>
-      <c r="AU16" s="66"/>
-      <c r="AV16" s="67"/>
-      <c r="AW16" s="67"/>
-      <c r="AX16" s="68"/>
-    </row>
-    <row r="17" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="81"/>
+      <c r="AC16" s="63"/>
+      <c r="AD16" s="64"/>
+      <c r="AE16" s="64"/>
+      <c r="AF16" s="64"/>
+      <c r="AG16" s="64"/>
+      <c r="AH16" s="64"/>
+      <c r="AI16" s="64"/>
+      <c r="AJ16" s="64"/>
+      <c r="AK16" s="64"/>
+      <c r="AL16" s="64"/>
+      <c r="AM16" s="64"/>
+      <c r="AN16" s="64"/>
+      <c r="AO16" s="64"/>
+      <c r="AP16" s="65"/>
+      <c r="AQ16" s="92"/>
+      <c r="AR16" s="93"/>
+      <c r="AS16" s="93"/>
+      <c r="AT16" s="94"/>
+      <c r="AU16" s="72"/>
+      <c r="AV16" s="73"/>
+      <c r="AW16" s="73"/>
+      <c r="AX16" s="74"/>
+    </row>
+    <row r="17" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="87"/>
       <c r="C17" s="57"/>
       <c r="D17" s="58"/>
       <c r="E17" s="58"/>
@@ -4357,31 +4357,31 @@
       <c r="Z17" s="58"/>
       <c r="AA17" s="58"/>
       <c r="AB17" s="59"/>
-      <c r="AC17" s="107"/>
-      <c r="AD17" s="108"/>
-      <c r="AE17" s="108"/>
-      <c r="AF17" s="108"/>
-      <c r="AG17" s="108"/>
-      <c r="AH17" s="108"/>
-      <c r="AI17" s="108"/>
-      <c r="AJ17" s="108"/>
-      <c r="AK17" s="108"/>
-      <c r="AL17" s="108"/>
-      <c r="AM17" s="108"/>
-      <c r="AN17" s="108"/>
-      <c r="AO17" s="108"/>
-      <c r="AP17" s="109"/>
-      <c r="AQ17" s="86"/>
-      <c r="AR17" s="87"/>
-      <c r="AS17" s="87"/>
-      <c r="AT17" s="88"/>
-      <c r="AU17" s="66"/>
-      <c r="AV17" s="67"/>
-      <c r="AW17" s="67"/>
-      <c r="AX17" s="68"/>
-    </row>
-    <row r="18" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="81"/>
+      <c r="AC17" s="63"/>
+      <c r="AD17" s="64"/>
+      <c r="AE17" s="64"/>
+      <c r="AF17" s="64"/>
+      <c r="AG17" s="64"/>
+      <c r="AH17" s="64"/>
+      <c r="AI17" s="64"/>
+      <c r="AJ17" s="64"/>
+      <c r="AK17" s="64"/>
+      <c r="AL17" s="64"/>
+      <c r="AM17" s="64"/>
+      <c r="AN17" s="64"/>
+      <c r="AO17" s="64"/>
+      <c r="AP17" s="65"/>
+      <c r="AQ17" s="92"/>
+      <c r="AR17" s="93"/>
+      <c r="AS17" s="93"/>
+      <c r="AT17" s="94"/>
+      <c r="AU17" s="72"/>
+      <c r="AV17" s="73"/>
+      <c r="AW17" s="73"/>
+      <c r="AX17" s="74"/>
+    </row>
+    <row r="18" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="87"/>
       <c r="C18" s="57"/>
       <c r="D18" s="58"/>
       <c r="E18" s="58"/>
@@ -4408,31 +4408,31 @@
       <c r="Z18" s="58"/>
       <c r="AA18" s="58"/>
       <c r="AB18" s="59"/>
-      <c r="AC18" s="107"/>
-      <c r="AD18" s="108"/>
-      <c r="AE18" s="108"/>
-      <c r="AF18" s="108"/>
-      <c r="AG18" s="108"/>
-      <c r="AH18" s="108"/>
-      <c r="AI18" s="108"/>
-      <c r="AJ18" s="108"/>
-      <c r="AK18" s="108"/>
-      <c r="AL18" s="108"/>
-      <c r="AM18" s="108"/>
-      <c r="AN18" s="108"/>
-      <c r="AO18" s="108"/>
-      <c r="AP18" s="109"/>
-      <c r="AQ18" s="86"/>
-      <c r="AR18" s="87"/>
-      <c r="AS18" s="87"/>
-      <c r="AT18" s="88"/>
-      <c r="AU18" s="66"/>
-      <c r="AV18" s="67"/>
-      <c r="AW18" s="67"/>
-      <c r="AX18" s="68"/>
-    </row>
-    <row r="19" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="81"/>
+      <c r="AC18" s="63"/>
+      <c r="AD18" s="64"/>
+      <c r="AE18" s="64"/>
+      <c r="AF18" s="64"/>
+      <c r="AG18" s="64"/>
+      <c r="AH18" s="64"/>
+      <c r="AI18" s="64"/>
+      <c r="AJ18" s="64"/>
+      <c r="AK18" s="64"/>
+      <c r="AL18" s="64"/>
+      <c r="AM18" s="64"/>
+      <c r="AN18" s="64"/>
+      <c r="AO18" s="64"/>
+      <c r="AP18" s="65"/>
+      <c r="AQ18" s="92"/>
+      <c r="AR18" s="93"/>
+      <c r="AS18" s="93"/>
+      <c r="AT18" s="94"/>
+      <c r="AU18" s="72"/>
+      <c r="AV18" s="73"/>
+      <c r="AW18" s="73"/>
+      <c r="AX18" s="74"/>
+    </row>
+    <row r="19" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="87"/>
       <c r="C19" s="57"/>
       <c r="D19" s="58"/>
       <c r="E19" s="58"/>
@@ -4459,31 +4459,31 @@
       <c r="Z19" s="58"/>
       <c r="AA19" s="58"/>
       <c r="AB19" s="59"/>
-      <c r="AC19" s="107"/>
-      <c r="AD19" s="108"/>
-      <c r="AE19" s="108"/>
-      <c r="AF19" s="108"/>
-      <c r="AG19" s="108"/>
-      <c r="AH19" s="108"/>
-      <c r="AI19" s="108"/>
-      <c r="AJ19" s="108"/>
-      <c r="AK19" s="108"/>
-      <c r="AL19" s="108"/>
-      <c r="AM19" s="108"/>
-      <c r="AN19" s="108"/>
-      <c r="AO19" s="108"/>
-      <c r="AP19" s="109"/>
-      <c r="AQ19" s="86"/>
-      <c r="AR19" s="87"/>
-      <c r="AS19" s="87"/>
-      <c r="AT19" s="88"/>
-      <c r="AU19" s="66"/>
-      <c r="AV19" s="67"/>
-      <c r="AW19" s="67"/>
-      <c r="AX19" s="68"/>
-    </row>
-    <row r="20" spans="2:50" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="82"/>
+      <c r="AC19" s="63"/>
+      <c r="AD19" s="64"/>
+      <c r="AE19" s="64"/>
+      <c r="AF19" s="64"/>
+      <c r="AG19" s="64"/>
+      <c r="AH19" s="64"/>
+      <c r="AI19" s="64"/>
+      <c r="AJ19" s="64"/>
+      <c r="AK19" s="64"/>
+      <c r="AL19" s="64"/>
+      <c r="AM19" s="64"/>
+      <c r="AN19" s="64"/>
+      <c r="AO19" s="64"/>
+      <c r="AP19" s="65"/>
+      <c r="AQ19" s="92"/>
+      <c r="AR19" s="93"/>
+      <c r="AS19" s="93"/>
+      <c r="AT19" s="94"/>
+      <c r="AU19" s="72"/>
+      <c r="AV19" s="73"/>
+      <c r="AW19" s="73"/>
+      <c r="AX19" s="74"/>
+    </row>
+    <row r="20" spans="2:50" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="88"/>
       <c r="C20" s="54"/>
       <c r="D20" s="55"/>
       <c r="E20" s="55"/>
@@ -4510,30 +4510,30 @@
       <c r="Z20" s="55"/>
       <c r="AA20" s="55"/>
       <c r="AB20" s="56"/>
-      <c r="AC20" s="92"/>
-      <c r="AD20" s="93"/>
-      <c r="AE20" s="93"/>
-      <c r="AF20" s="93"/>
-      <c r="AG20" s="93"/>
-      <c r="AH20" s="93"/>
-      <c r="AI20" s="93"/>
-      <c r="AJ20" s="93"/>
-      <c r="AK20" s="93"/>
-      <c r="AL20" s="93"/>
-      <c r="AM20" s="93"/>
-      <c r="AN20" s="93"/>
-      <c r="AO20" s="93"/>
-      <c r="AP20" s="94"/>
-      <c r="AQ20" s="89"/>
-      <c r="AR20" s="90"/>
-      <c r="AS20" s="90"/>
-      <c r="AT20" s="91"/>
-      <c r="AU20" s="69"/>
-      <c r="AV20" s="70"/>
-      <c r="AW20" s="70"/>
-      <c r="AX20" s="71"/>
-    </row>
-    <row r="21" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AC20" s="66"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="67"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="67"/>
+      <c r="AN20" s="67"/>
+      <c r="AO20" s="67"/>
+      <c r="AP20" s="68"/>
+      <c r="AQ20" s="95"/>
+      <c r="AR20" s="96"/>
+      <c r="AS20" s="96"/>
+      <c r="AT20" s="97"/>
+      <c r="AU20" s="75"/>
+      <c r="AV20" s="76"/>
+      <c r="AW20" s="76"/>
+      <c r="AX20" s="77"/>
+    </row>
+    <row r="21" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <v>11</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="AW21" s="7"/>
       <c r="AX21" s="8"/>
     </row>
-    <row r="22" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <v>12</v>
       </c>
@@ -4661,7 +4661,7 @@
       <c r="AW22" s="7"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <v>13</v>
       </c>
@@ -4726,7 +4726,7 @@
       <c r="AW23" s="7"/>
       <c r="AX23" s="8"/>
     </row>
-    <row r="24" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3">
         <v>14</v>
       </c>
@@ -4791,7 +4791,7 @@
       <c r="AW24" s="7"/>
       <c r="AX24" s="8"/>
     </row>
-    <row r="25" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3">
         <v>15</v>
       </c>
@@ -4856,7 +4856,7 @@
       <c r="AW25" s="7"/>
       <c r="AX25" s="8"/>
     </row>
-    <row r="26" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="3">
         <v>16</v>
       </c>
@@ -4921,7 +4921,7 @@
       <c r="AW26" s="7"/>
       <c r="AX26" s="8"/>
     </row>
-    <row r="27" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="3">
         <v>17</v>
       </c>
@@ -4986,7 +4986,7 @@
       <c r="AW27" s="7"/>
       <c r="AX27" s="8"/>
     </row>
-    <row r="28" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="3">
         <v>18</v>
       </c>
@@ -5051,7 +5051,7 @@
       <c r="AW28" s="7"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3">
         <v>19</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="AW29" s="7"/>
       <c r="AX29" s="8"/>
     </row>
-    <row r="30" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="3">
         <v>20</v>
       </c>
@@ -5181,7 +5181,7 @@
       <c r="AW30" s="7"/>
       <c r="AX30" s="8"/>
     </row>
-    <row r="31" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="3">
         <v>21</v>
       </c>
@@ -5246,7 +5246,7 @@
       <c r="AW31" s="7"/>
       <c r="AX31" s="8"/>
     </row>
-    <row r="32" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:50" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="3">
         <v>22</v>
       </c>
@@ -5309,7 +5309,7 @@
       <c r="AW32" s="7"/>
       <c r="AX32" s="8"/>
     </row>
-    <row r="33" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="3">
         <v>23</v>
       </c>
@@ -5374,7 +5374,7 @@
       <c r="AW33" s="7"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="3">
         <v>24</v>
       </c>
@@ -5437,7 +5437,7 @@
       <c r="AW34" s="7"/>
       <c r="AX34" s="8"/>
     </row>
-    <row r="35" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B35" s="3">
         <v>25</v>
       </c>
@@ -5502,7 +5502,7 @@
       <c r="AW35" s="7"/>
       <c r="AX35" s="8"/>
     </row>
-    <row r="36" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B36" s="3">
         <v>26</v>
       </c>
@@ -5567,8 +5567,8 @@
       <c r="AW36" s="7"/>
       <c r="AX36" s="8"/>
     </row>
-    <row r="37" spans="2:59" ht="17.45" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="80">
+    <row r="37" spans="2:59" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B37" s="86">
         <v>27</v>
       </c>
       <c r="C37" s="51" t="s">
@@ -5619,21 +5619,21 @@
       <c r="AN37" s="11"/>
       <c r="AO37" s="11"/>
       <c r="AP37" s="12"/>
-      <c r="AQ37" s="83">
+      <c r="AQ37" s="89">
         <v>45630</v>
       </c>
-      <c r="AR37" s="84"/>
-      <c r="AS37" s="84"/>
-      <c r="AT37" s="85"/>
-      <c r="AU37" s="63" t="s">
+      <c r="AR37" s="90"/>
+      <c r="AS37" s="90"/>
+      <c r="AT37" s="91"/>
+      <c r="AU37" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="AV37" s="64"/>
-      <c r="AW37" s="64"/>
-      <c r="AX37" s="65"/>
-    </row>
-    <row r="38" spans="2:59" ht="41.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="82"/>
+      <c r="AV37" s="70"/>
+      <c r="AW37" s="70"/>
+      <c r="AX37" s="71"/>
+    </row>
+    <row r="38" spans="2:59" ht="41.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="88"/>
       <c r="C38" s="54"/>
       <c r="D38" s="55"/>
       <c r="E38" s="55"/>
@@ -5643,23 +5643,23 @@
       <c r="I38" s="55"/>
       <c r="J38" s="55"/>
       <c r="K38" s="56"/>
-      <c r="L38" s="92"/>
-      <c r="M38" s="93"/>
-      <c r="N38" s="93"/>
-      <c r="O38" s="93"/>
-      <c r="P38" s="93"/>
-      <c r="Q38" s="93"/>
-      <c r="R38" s="93"/>
-      <c r="S38" s="93"/>
-      <c r="T38" s="93"/>
-      <c r="U38" s="93"/>
-      <c r="V38" s="93"/>
-      <c r="W38" s="93"/>
-      <c r="X38" s="93"/>
-      <c r="Y38" s="93"/>
-      <c r="Z38" s="93"/>
-      <c r="AA38" s="93"/>
-      <c r="AB38" s="94"/>
+      <c r="L38" s="66"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="67"/>
+      <c r="O38" s="67"/>
+      <c r="P38" s="67"/>
+      <c r="Q38" s="67"/>
+      <c r="R38" s="67"/>
+      <c r="S38" s="67"/>
+      <c r="T38" s="67"/>
+      <c r="U38" s="67"/>
+      <c r="V38" s="67"/>
+      <c r="W38" s="67"/>
+      <c r="X38" s="67"/>
+      <c r="Y38" s="67"/>
+      <c r="Z38" s="67"/>
+      <c r="AA38" s="67"/>
+      <c r="AB38" s="68"/>
       <c r="AC38" s="13"/>
       <c r="AD38" s="14"/>
       <c r="AE38" s="14"/>
@@ -5674,14 +5674,14 @@
       <c r="AN38" s="14"/>
       <c r="AO38" s="14"/>
       <c r="AP38" s="15"/>
-      <c r="AQ38" s="89"/>
-      <c r="AR38" s="90"/>
-      <c r="AS38" s="90"/>
-      <c r="AT38" s="91"/>
-      <c r="AU38" s="69"/>
-      <c r="AV38" s="70"/>
-      <c r="AW38" s="70"/>
-      <c r="AX38" s="71"/>
+      <c r="AQ38" s="95"/>
+      <c r="AR38" s="96"/>
+      <c r="AS38" s="96"/>
+      <c r="AT38" s="97"/>
+      <c r="AU38" s="75"/>
+      <c r="AV38" s="76"/>
+      <c r="AW38" s="76"/>
+      <c r="AX38" s="77"/>
       <c r="AY38" s="19" t="s">
         <v>121</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B39" s="3">
         <v>28</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:59" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B40" s="3">
         <v>29</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="2:59" ht="59.45" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:59" ht="59.4" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B41" s="3">
         <v>30</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="2:59" ht="55.9" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:59" ht="55.95" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B42" s="3">
         <v>31</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="2:59" ht="52.9" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:59" ht="52.95" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B43" s="3">
         <v>32</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="BA43" s="20"/>
       <c r="BB43" s="20"/>
     </row>
-    <row r="44" spans="2:59" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:59" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B44" s="3">
         <v>33</v>
       </c>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="BB44" s="17"/>
     </row>
-    <row r="45" spans="2:59" ht="45.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:59" ht="45.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B45" s="3">
         <v>34</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D45" s="26"/>
       <c r="E45" s="26"/>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="BB45" s="17"/>
     </row>
-    <row r="46" spans="2:59" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:59" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B46" s="3">
         <v>35</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="47" spans="2:59" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:59" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B47" s="3">
         <v>36</v>
       </c>
@@ -6371,12 +6371,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="2:59" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:59" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B48" s="3">
         <v>37</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D48" s="26"/>
       <c r="E48" s="26"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="BB48" s="17"/>
     </row>
-    <row r="49" spans="2:56" ht="34.9" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:56" ht="34.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B49" s="3">
         <v>38</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="2:56" ht="19.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:56" ht="19.2" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="3">
         <v>39</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="2:56" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:56" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="3">
         <v>40</v>
       </c>
@@ -6663,7 +6663,7 @@
       <c r="BA51" s="17"/>
       <c r="BB51" s="17"/>
     </row>
-    <row r="52" spans="2:56" ht="30.6" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:56" ht="30.6" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="3">
         <v>41</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="2:56" ht="61.15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:56" ht="61.2" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="3">
         <v>42</v>
       </c>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="BB53" s="17"/>
     </row>
-    <row r="54" spans="2:56" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:56" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="3">
         <v>43</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D54" s="26"/>
       <c r="E54" s="26"/>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="BB54" s="17"/>
     </row>
-    <row r="55" spans="2:56" ht="31.15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:56" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B55" s="3">
         <v>44</v>
       </c>
@@ -6957,7 +6957,7 @@
       <c r="BA55" s="17"/>
       <c r="BB55" s="17"/>
     </row>
-    <row r="56" spans="2:56" ht="34.9" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:56" ht="34.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="3">
         <v>45</v>
       </c>
@@ -7026,7 +7026,7 @@
       <c r="BA56" s="17"/>
       <c r="BB56" s="17"/>
     </row>
-    <row r="57" spans="2:56" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:56" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B57" s="3">
         <v>46</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="2:56" ht="48.6" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:56" ht="48.6" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B58" s="3">
         <v>47</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="59" spans="2:56" hidden="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:56" hidden="1" x14ac:dyDescent="0.45">
       <c r="B59" s="3">
         <v>48</v>
       </c>
@@ -7256,12 +7256,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="2:56" ht="120.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:56" ht="120.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B60" s="3">
         <v>49</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D60" s="26"/>
       <c r="E60" s="26"/>
@@ -7325,12 +7325,12 @@
       <c r="BA60" s="17"/>
       <c r="BB60" s="17"/>
     </row>
-    <row r="61" spans="2:56" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:56" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B61" s="3">
         <v>50</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="26"/>
       <c r="E61" s="26"/>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="BB61" s="17"/>
     </row>
-    <row r="62" spans="2:56" ht="36.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:56" ht="36.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B62" s="3">
         <v>51</v>
       </c>
@@ -7477,7 +7477,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="63" spans="2:56" ht="72.599999999999994" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:56" ht="72.599999999999994" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B63" s="3">
         <v>52</v>
       </c>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="BB63" s="17"/>
     </row>
-    <row r="64" spans="2:56" ht="81" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:56" ht="81" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B64" s="3">
         <v>53</v>
       </c>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BB64" s="17"/>
     </row>
-    <row r="65" spans="2:54" ht="84" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:54" ht="84" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B65" s="3">
         <v>54</v>
       </c>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="BB65" s="17"/>
     </row>
-    <row r="66" spans="2:54" ht="40.15" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:54" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B66" s="3">
         <v>55</v>
       </c>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="BB66" s="17"/>
     </row>
-    <row r="67" spans="2:54" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:54" ht="48.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="3">
         <v>56</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" s="26"/>
       <c r="E67" s="26"/>
@@ -7914,7 +7914,7 @@
       <c r="AW67" s="7"/>
       <c r="AX67" s="8"/>
     </row>
-    <row r="68" spans="2:54" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:54" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B68" s="3">
         <v>57</v>
       </c>
@@ -7982,10 +7982,10 @@
         <v>187</v>
       </c>
     </row>
-    <row r="69" spans="2:54" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="70" spans="2:54" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="71" spans="2:54" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="73" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:54" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="70" spans="2:54" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="71" spans="2:54" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="73" spans="2:54" x14ac:dyDescent="0.45">
       <c r="B73" s="1" t="s">
         <v>186</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="74" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:54" x14ac:dyDescent="0.45">
       <c r="B74" s="1" t="s">
         <v>188</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="75" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:54" x14ac:dyDescent="0.45">
       <c r="B75" s="1" t="s">
         <v>191</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="76" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:54" x14ac:dyDescent="0.45">
       <c r="B76" s="1" t="s">
         <v>195</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="77" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:54" x14ac:dyDescent="0.45">
       <c r="B77" s="1" t="s">
         <v>196</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="78" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:54" x14ac:dyDescent="0.45">
       <c r="B78" s="1" t="s">
         <v>197</v>
       </c>
@@ -8033,12 +8033,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="79" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:54" x14ac:dyDescent="0.45">
       <c r="F79" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="80" spans="2:54" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:54" x14ac:dyDescent="0.45">
       <c r="F80" s="1" t="s">
         <v>200</v>
       </c>
@@ -8344,134 +8344,134 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BBDF00-4B84-4D1F-8377-830822A914EE}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AY69"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.33203125" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="1"/>
-    <col min="2" max="2" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="45" width="3.28515625" style="1"/>
-    <col min="46" max="16384" width="3.28515625" style="2"/>
+    <col min="1" max="1" width="3.33203125" style="1"/>
+    <col min="2" max="2" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="45" width="3.33203125" style="1"/>
+    <col min="46" max="16384" width="3.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="AY1" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="72" t="s">
+    <row r="2" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72" t="s">
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72" t="s">
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="Y2" s="72"/>
-      <c r="Z2" s="72"/>
-      <c r="AA2" s="72"/>
-      <c r="AB2" s="72"/>
-      <c r="AC2" s="72"/>
-      <c r="AD2" s="72"/>
-      <c r="AE2" s="72"/>
-      <c r="AF2" s="72"/>
-      <c r="AG2" s="72"/>
-      <c r="AH2" s="72"/>
-      <c r="AI2" s="72"/>
-      <c r="AJ2" s="72"/>
-      <c r="AK2" s="72"/>
-      <c r="AL2" s="72"/>
-      <c r="AM2" s="72"/>
-      <c r="AN2" s="72" t="s">
+      <c r="Y2" s="78"/>
+      <c r="Z2" s="78"/>
+      <c r="AA2" s="78"/>
+      <c r="AB2" s="78"/>
+      <c r="AC2" s="78"/>
+      <c r="AD2" s="78"/>
+      <c r="AE2" s="78"/>
+      <c r="AF2" s="78"/>
+      <c r="AG2" s="78"/>
+      <c r="AH2" s="78"/>
+      <c r="AI2" s="78"/>
+      <c r="AJ2" s="78"/>
+      <c r="AK2" s="78"/>
+      <c r="AL2" s="78"/>
+      <c r="AM2" s="78"/>
+      <c r="AN2" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="AO2" s="72"/>
-      <c r="AP2" s="72"/>
-      <c r="AQ2" s="72"/>
-      <c r="AR2" s="72" t="s">
+      <c r="AO2" s="78"/>
+      <c r="AP2" s="78"/>
+      <c r="AQ2" s="78"/>
+      <c r="AR2" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="AS2" s="72"/>
-      <c r="AT2" s="72"/>
-      <c r="AU2" s="72"/>
+      <c r="AS2" s="78"/>
+      <c r="AT2" s="78"/>
+      <c r="AU2" s="78"/>
       <c r="AY2" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:51" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="72"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="72"/>
-      <c r="AK3" s="72"/>
-      <c r="AL3" s="72"/>
-      <c r="AM3" s="72"/>
-      <c r="AN3" s="72"/>
-      <c r="AO3" s="72"/>
-      <c r="AP3" s="72"/>
-      <c r="AQ3" s="72"/>
-      <c r="AR3" s="72"/>
-      <c r="AS3" s="72"/>
-      <c r="AT3" s="72"/>
-      <c r="AU3" s="72"/>
+    <row r="3" spans="2:51" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
+      <c r="Z3" s="78"/>
+      <c r="AA3" s="78"/>
+      <c r="AB3" s="78"/>
+      <c r="AC3" s="78"/>
+      <c r="AD3" s="78"/>
+      <c r="AE3" s="78"/>
+      <c r="AF3" s="78"/>
+      <c r="AG3" s="78"/>
+      <c r="AH3" s="78"/>
+      <c r="AI3" s="78"/>
+      <c r="AJ3" s="78"/>
+      <c r="AK3" s="78"/>
+      <c r="AL3" s="78"/>
+      <c r="AM3" s="78"/>
+      <c r="AN3" s="78"/>
+      <c r="AO3" s="78"/>
+      <c r="AP3" s="78"/>
+      <c r="AQ3" s="78"/>
+      <c r="AR3" s="78"/>
+      <c r="AS3" s="78"/>
+      <c r="AT3" s="78"/>
+      <c r="AU3" s="78"/>
       <c r="AY3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3">
         <v>2</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3">
         <v>3</v>
       </c>
@@ -8655,7 +8655,7 @@
       <c r="AT6" s="5"/>
       <c r="AU6" s="6"/>
     </row>
-    <row r="7" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="3">
         <v>4</v>
       </c>
@@ -8713,7 +8713,7 @@
       <c r="AT7" s="5"/>
       <c r="AU7" s="6"/>
     </row>
-    <row r="8" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="3">
         <v>5</v>
       </c>
@@ -8771,7 +8771,7 @@
       <c r="AT8" s="5"/>
       <c r="AU8" s="6"/>
     </row>
-    <row r="9" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="3">
         <v>6</v>
       </c>
@@ -8829,7 +8829,7 @@
       <c r="AT9" s="5"/>
       <c r="AU9" s="6"/>
     </row>
-    <row r="10" spans="2:51" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:51" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="3">
         <v>7</v>
       </c>
@@ -8889,7 +8889,7 @@
       <c r="AT10" s="5"/>
       <c r="AU10" s="6"/>
     </row>
-    <row r="11" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="3">
         <v>8</v>
       </c>
@@ -8947,7 +8947,7 @@
       <c r="AT11" s="5"/>
       <c r="AU11" s="6"/>
     </row>
-    <row r="12" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="3">
         <v>9</v>
       </c>
@@ -9007,7 +9007,7 @@
       <c r="AT12" s="5"/>
       <c r="AU12" s="6"/>
     </row>
-    <row r="13" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
         <v>10</v>
       </c>
@@ -9065,8 +9065,8 @@
       <c r="AT13" s="5"/>
       <c r="AU13" s="6"/>
     </row>
-    <row r="14" spans="2:51" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="80">
+    <row r="14" spans="2:51" ht="16.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="86">
         <v>11</v>
       </c>
       <c r="C14" s="51" t="s">
@@ -9110,42 +9110,42 @@
       <c r="AK14" s="5"/>
       <c r="AL14" s="5"/>
       <c r="AM14" s="6"/>
-      <c r="AN14" s="83">
+      <c r="AN14" s="89">
         <v>45631</v>
       </c>
-      <c r="AO14" s="84"/>
-      <c r="AP14" s="84"/>
-      <c r="AQ14" s="85"/>
-      <c r="AR14" s="63" t="s">
+      <c r="AO14" s="90"/>
+      <c r="AP14" s="90"/>
+      <c r="AQ14" s="91"/>
+      <c r="AR14" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="AS14" s="64"/>
-      <c r="AT14" s="64"/>
-      <c r="AU14" s="65"/>
-    </row>
-    <row r="15" spans="2:51" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="82"/>
+      <c r="AS14" s="70"/>
+      <c r="AT14" s="70"/>
+      <c r="AU14" s="71"/>
+    </row>
+    <row r="15" spans="2:51" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="88"/>
       <c r="C15" s="54"/>
       <c r="D15" s="55"/>
       <c r="E15" s="55"/>
       <c r="F15" s="56"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="93"/>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="93"/>
-      <c r="P15" s="93"/>
-      <c r="Q15" s="93"/>
-      <c r="R15" s="93"/>
-      <c r="S15" s="93"/>
-      <c r="T15" s="93"/>
-      <c r="U15" s="93"/>
-      <c r="V15" s="93"/>
-      <c r="W15" s="94"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="68"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
@@ -9162,17 +9162,17 @@
       <c r="AK15" s="5"/>
       <c r="AL15" s="5"/>
       <c r="AM15" s="6"/>
-      <c r="AN15" s="89"/>
-      <c r="AO15" s="90"/>
-      <c r="AP15" s="90"/>
-      <c r="AQ15" s="91"/>
-      <c r="AR15" s="69"/>
-      <c r="AS15" s="70"/>
-      <c r="AT15" s="70"/>
-      <c r="AU15" s="71"/>
-    </row>
-    <row r="16" spans="2:51" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="80">
+      <c r="AN15" s="95"/>
+      <c r="AO15" s="96"/>
+      <c r="AP15" s="96"/>
+      <c r="AQ15" s="97"/>
+      <c r="AR15" s="75"/>
+      <c r="AS15" s="76"/>
+      <c r="AT15" s="76"/>
+      <c r="AU15" s="77"/>
+    </row>
+    <row r="16" spans="2:51" ht="16.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="86">
         <v>12</v>
       </c>
       <c r="C16" s="51" t="s">
@@ -9216,42 +9216,42 @@
       <c r="AK16" s="5"/>
       <c r="AL16" s="5"/>
       <c r="AM16" s="6"/>
-      <c r="AN16" s="83">
+      <c r="AN16" s="89">
         <v>45631</v>
       </c>
-      <c r="AO16" s="84"/>
-      <c r="AP16" s="84"/>
-      <c r="AQ16" s="85"/>
-      <c r="AR16" s="63" t="s">
+      <c r="AO16" s="90"/>
+      <c r="AP16" s="90"/>
+      <c r="AQ16" s="91"/>
+      <c r="AR16" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="AS16" s="64"/>
-      <c r="AT16" s="64"/>
-      <c r="AU16" s="65"/>
-    </row>
-    <row r="17" spans="2:47" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="82"/>
+      <c r="AS16" s="70"/>
+      <c r="AT16" s="70"/>
+      <c r="AU16" s="71"/>
+    </row>
+    <row r="17" spans="2:47" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="88"/>
       <c r="C17" s="54"/>
       <c r="D17" s="55"/>
       <c r="E17" s="55"/>
       <c r="F17" s="56"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="93"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="93"/>
-      <c r="R17" s="93"/>
-      <c r="S17" s="93"/>
-      <c r="T17" s="93"/>
-      <c r="U17" s="93"/>
-      <c r="V17" s="93"/>
-      <c r="W17" s="94"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="68"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
@@ -9268,16 +9268,16 @@
       <c r="AK17" s="5"/>
       <c r="AL17" s="5"/>
       <c r="AM17" s="6"/>
-      <c r="AN17" s="89"/>
-      <c r="AO17" s="90"/>
-      <c r="AP17" s="90"/>
-      <c r="AQ17" s="91"/>
-      <c r="AR17" s="69"/>
-      <c r="AS17" s="70"/>
-      <c r="AT17" s="70"/>
-      <c r="AU17" s="71"/>
-    </row>
-    <row r="18" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AN17" s="95"/>
+      <c r="AO17" s="96"/>
+      <c r="AP17" s="96"/>
+      <c r="AQ17" s="97"/>
+      <c r="AR17" s="75"/>
+      <c r="AS17" s="76"/>
+      <c r="AT17" s="76"/>
+      <c r="AU17" s="77"/>
+    </row>
+    <row r="18" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3">
         <v>13</v>
       </c>
@@ -9337,7 +9337,7 @@
       <c r="AT18" s="5"/>
       <c r="AU18" s="6"/>
     </row>
-    <row r="19" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3">
         <v>14</v>
       </c>
@@ -9395,7 +9395,7 @@
       <c r="AT19" s="5"/>
       <c r="AU19" s="6"/>
     </row>
-    <row r="20" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
         <v>15</v>
       </c>
@@ -9453,7 +9453,7 @@
       <c r="AT20" s="5"/>
       <c r="AU20" s="6"/>
     </row>
-    <row r="21" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <v>16</v>
       </c>
@@ -9511,7 +9511,7 @@
       <c r="AT21" s="5"/>
       <c r="AU21" s="6"/>
     </row>
-    <row r="22" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <v>17</v>
       </c>
@@ -9569,12 +9569,12 @@
       <c r="AT22" s="5"/>
       <c r="AU22" s="6"/>
     </row>
-    <row r="23" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <v>18</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
@@ -9629,7 +9629,7 @@
       <c r="AT23" s="5"/>
       <c r="AU23" s="6"/>
     </row>
-    <row r="24" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3">
         <v>19</v>
       </c>
@@ -9687,7 +9687,7 @@
       <c r="AT24" s="5"/>
       <c r="AU24" s="6"/>
     </row>
-    <row r="25" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3">
         <v>20</v>
       </c>
@@ -9745,8 +9745,8 @@
       <c r="AT25" s="5"/>
       <c r="AU25" s="6"/>
     </row>
-    <row r="26" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="104">
+    <row r="26" spans="2:47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="107">
         <v>21</v>
       </c>
       <c r="C26" s="51" t="s">
@@ -9755,153 +9755,153 @@
       <c r="D26" s="52"/>
       <c r="E26" s="52"/>
       <c r="F26" s="53"/>
-      <c r="G26" s="63" t="s">
+      <c r="G26" s="69" t="s">
         <v>179</v>
       </c>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="64"/>
-      <c r="R26" s="64"/>
-      <c r="S26" s="64"/>
-      <c r="T26" s="64"/>
-      <c r="U26" s="64"/>
-      <c r="V26" s="64"/>
-      <c r="W26" s="65"/>
-      <c r="X26" s="95" t="s">
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="70"/>
+      <c r="R26" s="70"/>
+      <c r="S26" s="70"/>
+      <c r="T26" s="70"/>
+      <c r="U26" s="70"/>
+      <c r="V26" s="70"/>
+      <c r="W26" s="71"/>
+      <c r="X26" s="98" t="s">
         <v>180</v>
       </c>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="96"/>
-      <c r="AA26" s="96"/>
-      <c r="AB26" s="96"/>
-      <c r="AC26" s="96"/>
-      <c r="AD26" s="96"/>
-      <c r="AE26" s="96"/>
-      <c r="AF26" s="96"/>
-      <c r="AG26" s="96"/>
-      <c r="AH26" s="96"/>
-      <c r="AI26" s="96"/>
-      <c r="AJ26" s="96"/>
-      <c r="AK26" s="96"/>
-      <c r="AL26" s="96"/>
-      <c r="AM26" s="97"/>
-      <c r="AN26" s="83">
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="99"/>
+      <c r="AA26" s="99"/>
+      <c r="AB26" s="99"/>
+      <c r="AC26" s="99"/>
+      <c r="AD26" s="99"/>
+      <c r="AE26" s="99"/>
+      <c r="AF26" s="99"/>
+      <c r="AG26" s="99"/>
+      <c r="AH26" s="99"/>
+      <c r="AI26" s="99"/>
+      <c r="AJ26" s="99"/>
+      <c r="AK26" s="99"/>
+      <c r="AL26" s="99"/>
+      <c r="AM26" s="100"/>
+      <c r="AN26" s="89">
         <v>45747</v>
       </c>
-      <c r="AO26" s="84"/>
-      <c r="AP26" s="84"/>
-      <c r="AQ26" s="85"/>
-      <c r="AR26" s="63" t="s">
+      <c r="AO26" s="90"/>
+      <c r="AP26" s="90"/>
+      <c r="AQ26" s="91"/>
+      <c r="AR26" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="AS26" s="64"/>
-      <c r="AT26" s="64"/>
-      <c r="AU26" s="65"/>
-    </row>
-    <row r="27" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="105"/>
+      <c r="AS26" s="70"/>
+      <c r="AT26" s="70"/>
+      <c r="AU26" s="71"/>
+    </row>
+    <row r="27" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="108"/>
       <c r="C27" s="57"/>
       <c r="D27" s="58"/>
       <c r="E27" s="58"/>
       <c r="F27" s="59"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="67"/>
-      <c r="R27" s="67"/>
-      <c r="S27" s="67"/>
-      <c r="T27" s="67"/>
-      <c r="U27" s="67"/>
-      <c r="V27" s="67"/>
-      <c r="W27" s="68"/>
-      <c r="X27" s="98"/>
-      <c r="Y27" s="99"/>
-      <c r="Z27" s="99"/>
-      <c r="AA27" s="99"/>
-      <c r="AB27" s="99"/>
-      <c r="AC27" s="99"/>
-      <c r="AD27" s="99"/>
-      <c r="AE27" s="99"/>
-      <c r="AF27" s="99"/>
-      <c r="AG27" s="99"/>
-      <c r="AH27" s="99"/>
-      <c r="AI27" s="99"/>
-      <c r="AJ27" s="99"/>
-      <c r="AK27" s="99"/>
-      <c r="AL27" s="99"/>
-      <c r="AM27" s="100"/>
-      <c r="AN27" s="86"/>
-      <c r="AO27" s="87"/>
-      <c r="AP27" s="87"/>
-      <c r="AQ27" s="88"/>
-      <c r="AR27" s="66"/>
-      <c r="AS27" s="67"/>
-      <c r="AT27" s="67"/>
-      <c r="AU27" s="68"/>
-    </row>
-    <row r="28" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="106"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="73"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="73"/>
+      <c r="O27" s="73"/>
+      <c r="P27" s="73"/>
+      <c r="Q27" s="73"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="73"/>
+      <c r="T27" s="73"/>
+      <c r="U27" s="73"/>
+      <c r="V27" s="73"/>
+      <c r="W27" s="74"/>
+      <c r="X27" s="101"/>
+      <c r="Y27" s="102"/>
+      <c r="Z27" s="102"/>
+      <c r="AA27" s="102"/>
+      <c r="AB27" s="102"/>
+      <c r="AC27" s="102"/>
+      <c r="AD27" s="102"/>
+      <c r="AE27" s="102"/>
+      <c r="AF27" s="102"/>
+      <c r="AG27" s="102"/>
+      <c r="AH27" s="102"/>
+      <c r="AI27" s="102"/>
+      <c r="AJ27" s="102"/>
+      <c r="AK27" s="102"/>
+      <c r="AL27" s="102"/>
+      <c r="AM27" s="103"/>
+      <c r="AN27" s="92"/>
+      <c r="AO27" s="93"/>
+      <c r="AP27" s="93"/>
+      <c r="AQ27" s="94"/>
+      <c r="AR27" s="72"/>
+      <c r="AS27" s="73"/>
+      <c r="AT27" s="73"/>
+      <c r="AU27" s="74"/>
+    </row>
+    <row r="28" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="109"/>
       <c r="C28" s="54"/>
       <c r="D28" s="55"/>
       <c r="E28" s="55"/>
       <c r="F28" s="56"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="70"/>
-      <c r="R28" s="70"/>
-      <c r="S28" s="70"/>
-      <c r="T28" s="70"/>
-      <c r="U28" s="70"/>
-      <c r="V28" s="70"/>
-      <c r="W28" s="71"/>
-      <c r="X28" s="101"/>
-      <c r="Y28" s="102"/>
-      <c r="Z28" s="102"/>
-      <c r="AA28" s="102"/>
-      <c r="AB28" s="102"/>
-      <c r="AC28" s="102"/>
-      <c r="AD28" s="102"/>
-      <c r="AE28" s="102"/>
-      <c r="AF28" s="102"/>
-      <c r="AG28" s="102"/>
-      <c r="AH28" s="102"/>
-      <c r="AI28" s="102"/>
-      <c r="AJ28" s="102"/>
-      <c r="AK28" s="102"/>
-      <c r="AL28" s="102"/>
-      <c r="AM28" s="103"/>
-      <c r="AN28" s="89"/>
-      <c r="AO28" s="90"/>
-      <c r="AP28" s="90"/>
-      <c r="AQ28" s="91"/>
-      <c r="AR28" s="69"/>
-      <c r="AS28" s="70"/>
-      <c r="AT28" s="70"/>
-      <c r="AU28" s="71"/>
-    </row>
-    <row r="29" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G28" s="75"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="76"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="76"/>
+      <c r="Q28" s="76"/>
+      <c r="R28" s="76"/>
+      <c r="S28" s="76"/>
+      <c r="T28" s="76"/>
+      <c r="U28" s="76"/>
+      <c r="V28" s="76"/>
+      <c r="W28" s="77"/>
+      <c r="X28" s="104"/>
+      <c r="Y28" s="105"/>
+      <c r="Z28" s="105"/>
+      <c r="AA28" s="105"/>
+      <c r="AB28" s="105"/>
+      <c r="AC28" s="105"/>
+      <c r="AD28" s="105"/>
+      <c r="AE28" s="105"/>
+      <c r="AF28" s="105"/>
+      <c r="AG28" s="105"/>
+      <c r="AH28" s="105"/>
+      <c r="AI28" s="105"/>
+      <c r="AJ28" s="105"/>
+      <c r="AK28" s="105"/>
+      <c r="AL28" s="105"/>
+      <c r="AM28" s="106"/>
+      <c r="AN28" s="95"/>
+      <c r="AO28" s="96"/>
+      <c r="AP28" s="96"/>
+      <c r="AQ28" s="97"/>
+      <c r="AR28" s="75"/>
+      <c r="AS28" s="76"/>
+      <c r="AT28" s="76"/>
+      <c r="AU28" s="77"/>
+    </row>
+    <row r="29" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3">
         <v>22</v>
       </c>
@@ -9951,7 +9951,7 @@
       <c r="AT29" s="5"/>
       <c r="AU29" s="6"/>
     </row>
-    <row r="30" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="3">
         <v>23</v>
       </c>
@@ -10001,7 +10001,7 @@
       <c r="AT30" s="5"/>
       <c r="AU30" s="6"/>
     </row>
-    <row r="31" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="3">
         <v>24</v>
       </c>
@@ -10051,7 +10051,7 @@
       <c r="AT31" s="5"/>
       <c r="AU31" s="6"/>
     </row>
-    <row r="32" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:47" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="3">
         <v>25</v>
       </c>
@@ -10101,43 +10101,43 @@
       <c r="AT32" s="5"/>
       <c r="AU32" s="6"/>
     </row>
-    <row r="33" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="43" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="65" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="66" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="67" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="68" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="69" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="33" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="34" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="35" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="36" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="37" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="38" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="39" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="42" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="44" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="45" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="46" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="47" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="48" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="51" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="52" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="53" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="54" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="55" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="56" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="57" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="65" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="66" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="67" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="68" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="69" ht="14.1" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <autoFilter ref="B2:AU32" xr:uid="{95BBDF00-4B84-4D1F-8377-830822A914EE}">
     <filterColumn colId="1" showButton="0">
